--- a/excel_files/6_demand_change.xlsx
+++ b/excel_files/6_demand_change.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Hussam Daigham\Documents\SQL_Project_Data_Job_Analysis\excel_files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{93E97681-C75C-4D7D-A71F-9DEEF0ABBF8A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C06620C3-2FBC-4C9F-8562-A367CCFFF19E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{8AFD7F27-C0FF-4BA3-979A-E2267542220F}"/>
   </bookViews>
@@ -149,9 +149,8 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
@@ -211,9 +210,10 @@
               </a:defRPr>
             </a:pPr>
             <a:r>
-              <a:rPr lang="en-US" sz="1800" b="1"/>
-              <a:t>Percentage change in demand for the top 5 data analyst skills</a:t>
+              <a:rPr lang="en-US" sz="1800" b="1" i="0" u="none" strike="noStrike" baseline="0"/>
+              <a:t>Quarterly Demand Share for the Top 5 Data Analyst Skills</a:t>
             </a:r>
+            <a:endParaRPr lang="en-US" sz="2400" b="1"/>
           </a:p>
         </c:rich>
       </c:tx>
@@ -1841,10 +1841,10 @@
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A2" s="1" t="s">
+      <c r="A2" t="s">
         <v>6</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="B2" t="s">
         <v>7</v>
       </c>
       <c r="C2">
@@ -1855,10 +1855,10 @@
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A3" s="1" t="s">
+      <c r="A3" t="s">
         <v>6</v>
       </c>
-      <c r="B3" s="1" t="s">
+      <c r="B3" t="s">
         <v>8</v>
       </c>
       <c r="C3">
@@ -1869,10 +1869,10 @@
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A4" s="1" t="s">
+      <c r="A4" t="s">
         <v>6</v>
       </c>
-      <c r="B4" s="1" t="s">
+      <c r="B4" t="s">
         <v>9</v>
       </c>
       <c r="C4">
@@ -1883,10 +1883,10 @@
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A5" s="1" t="s">
+      <c r="A5" t="s">
         <v>6</v>
       </c>
-      <c r="B5" s="1" t="s">
+      <c r="B5" t="s">
         <v>10</v>
       </c>
       <c r="C5">
@@ -1897,10 +1897,10 @@
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A6" s="1" t="s">
+      <c r="A6" t="s">
         <v>6</v>
       </c>
-      <c r="B6" s="1" t="s">
+      <c r="B6" t="s">
         <v>11</v>
       </c>
       <c r="C6">
@@ -1911,10 +1911,10 @@
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A7" s="1" t="s">
+      <c r="A7" t="s">
         <v>12</v>
       </c>
-      <c r="B7" s="1" t="s">
+      <c r="B7" t="s">
         <v>7</v>
       </c>
       <c r="C7">
@@ -1931,10 +1931,10 @@
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A8" s="1" t="s">
+      <c r="A8" t="s">
         <v>12</v>
       </c>
-      <c r="B8" s="1" t="s">
+      <c r="B8" t="s">
         <v>8</v>
       </c>
       <c r="C8">
@@ -1951,10 +1951,10 @@
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A9" s="1" t="s">
+      <c r="A9" t="s">
         <v>12</v>
       </c>
-      <c r="B9" s="1" t="s">
+      <c r="B9" t="s">
         <v>9</v>
       </c>
       <c r="C9">
@@ -1971,10 +1971,10 @@
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A10" s="1" t="s">
+      <c r="A10" t="s">
         <v>12</v>
       </c>
-      <c r="B10" s="1" t="s">
+      <c r="B10" t="s">
         <v>10</v>
       </c>
       <c r="C10">
@@ -1991,10 +1991,10 @@
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A11" s="1" t="s">
+      <c r="A11" t="s">
         <v>12</v>
       </c>
-      <c r="B11" s="1" t="s">
+      <c r="B11" t="s">
         <v>11</v>
       </c>
       <c r="C11">
@@ -2011,10 +2011,10 @@
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A12" s="1" t="s">
+      <c r="A12" t="s">
         <v>13</v>
       </c>
-      <c r="B12" s="1" t="s">
+      <c r="B12" t="s">
         <v>7</v>
       </c>
       <c r="C12">
@@ -2031,10 +2031,10 @@
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A13" s="1" t="s">
+      <c r="A13" t="s">
         <v>13</v>
       </c>
-      <c r="B13" s="1" t="s">
+      <c r="B13" t="s">
         <v>8</v>
       </c>
       <c r="C13">
@@ -2051,10 +2051,10 @@
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A14" s="1" t="s">
+      <c r="A14" t="s">
         <v>13</v>
       </c>
-      <c r="B14" s="1" t="s">
+      <c r="B14" t="s">
         <v>9</v>
       </c>
       <c r="C14">
@@ -2071,10 +2071,10 @@
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A15" s="1" t="s">
+      <c r="A15" t="s">
         <v>13</v>
       </c>
-      <c r="B15" s="1" t="s">
+      <c r="B15" t="s">
         <v>10</v>
       </c>
       <c r="C15">
@@ -2091,10 +2091,10 @@
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A16" s="1" t="s">
+      <c r="A16" t="s">
         <v>13</v>
       </c>
-      <c r="B16" s="1" t="s">
+      <c r="B16" t="s">
         <v>11</v>
       </c>
       <c r="C16">
@@ -2111,10 +2111,10 @@
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A17" s="1" t="s">
+      <c r="A17" t="s">
         <v>14</v>
       </c>
-      <c r="B17" s="1" t="s">
+      <c r="B17" t="s">
         <v>7</v>
       </c>
       <c r="C17">
@@ -2131,10 +2131,10 @@
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A18" s="1" t="s">
+      <c r="A18" t="s">
         <v>14</v>
       </c>
-      <c r="B18" s="1" t="s">
+      <c r="B18" t="s">
         <v>8</v>
       </c>
       <c r="C18">
@@ -2151,10 +2151,10 @@
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A19" s="1" t="s">
+      <c r="A19" t="s">
         <v>14</v>
       </c>
-      <c r="B19" s="1" t="s">
+      <c r="B19" t="s">
         <v>9</v>
       </c>
       <c r="C19">
@@ -2171,10 +2171,10 @@
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A20" s="1" t="s">
+      <c r="A20" t="s">
         <v>14</v>
       </c>
-      <c r="B20" s="1" t="s">
+      <c r="B20" t="s">
         <v>10</v>
       </c>
       <c r="C20">
@@ -2191,10 +2191,10 @@
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A21" s="1" t="s">
+      <c r="A21" t="s">
         <v>14</v>
       </c>
-      <c r="B21" s="1" t="s">
+      <c r="B21" t="s">
         <v>11</v>
       </c>
       <c r="C21">
@@ -2234,19 +2234,19 @@
       <c r="A26" t="s">
         <v>6</v>
       </c>
-      <c r="B26" s="2">
+      <c r="B26" s="1">
         <v>0.48170000000000002</v>
       </c>
-      <c r="C26" s="2">
+      <c r="C26" s="1">
         <v>0.34810000000000002</v>
       </c>
-      <c r="D26" s="2">
+      <c r="D26" s="1">
         <v>0.28549999999999998</v>
       </c>
-      <c r="E26" s="2">
+      <c r="E26" s="1">
         <v>0.2412</v>
       </c>
-      <c r="F26" s="2">
+      <c r="F26" s="1">
         <v>0.191</v>
       </c>
     </row>
@@ -2254,19 +2254,19 @@
       <c r="A27" t="s">
         <v>12</v>
       </c>
-      <c r="B27" s="2">
+      <c r="B27" s="1">
         <v>0.48399999999999999</v>
       </c>
-      <c r="C27" s="2">
+      <c r="C27" s="1">
         <v>0.35580000000000001</v>
       </c>
-      <c r="D27" s="2">
+      <c r="D27" s="1">
         <v>0.29609999999999997</v>
       </c>
-      <c r="E27" s="2">
+      <c r="E27" s="1">
         <v>0.24099999999999999</v>
       </c>
-      <c r="F27" s="2">
+      <c r="F27" s="1">
         <v>0.20269999999999999</v>
       </c>
     </row>
@@ -2274,19 +2274,19 @@
       <c r="A28" t="s">
         <v>13</v>
       </c>
-      <c r="B28" s="2">
+      <c r="B28" s="1">
         <v>0.46899999999999997</v>
       </c>
-      <c r="C28" s="2">
+      <c r="C28" s="1">
         <v>0.33850000000000002</v>
       </c>
-      <c r="D28" s="2">
+      <c r="D28" s="1">
         <v>0.29499999999999998</v>
       </c>
-      <c r="E28" s="2">
+      <c r="E28" s="1">
         <v>0.23880000000000001</v>
       </c>
-      <c r="F28" s="2">
+      <c r="F28" s="1">
         <v>0.20730000000000001</v>
       </c>
     </row>
@@ -2294,19 +2294,19 @@
       <c r="A29" t="s">
         <v>14</v>
       </c>
-      <c r="B29" s="2">
+      <c r="B29" s="1">
         <v>0.44790000000000002</v>
       </c>
-      <c r="C29" s="2">
+      <c r="C29" s="1">
         <v>0.32019999999999998</v>
       </c>
-      <c r="D29" s="2">
+      <c r="D29" s="1">
         <v>0.29099999999999998</v>
       </c>
-      <c r="E29" s="2">
+      <c r="E29" s="1">
         <v>0.22500000000000001</v>
       </c>
-      <c r="F29" s="2">
+      <c r="F29" s="1">
         <v>0.20380000000000001</v>
       </c>
     </row>
